--- a/education_forms/032_historical_camps_knowledge_quiz--education_forms.xlsx
+++ b/education_forms/032_historical_camps_knowledge_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>first_historical_camp_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>What was the name of the first historical camp?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>first_historical_camp_date</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>In which century did the first historical camp appear?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>rome_camp_type</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>Which type of historical camp was used in the Roman Empire?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page_4</t>
+          <t>primary_purpose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>What was the primary purpose of historical camps in ancient civilizations?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_5</t>
+          <t>largest_historical_camp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>Which historical camp is the largest in the world?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_6</t>
+          <t>material_used</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>What is the main material used to construct historical camps?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_7</t>
+          <t>hill_camp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>Which historical camp was built on a hill?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_8</t>
+          <t>number_of_camps</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>What is the approximate number of historical camps existing today?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page_9</t>
+          <t>shape_camp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>What is the typical shape of a historical camp?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_10</t>
+          <t>agricultural_tool</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>Which historical camp is used as an agricultural tool?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page_11</t>
+          <t>age_of_camps</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>What is the average age of historical camps in years?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page_12</t>
+          <t>camps_per_km2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>How many historical camps are there per square kilometer?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page_13</t>
+          <t>ceremonial_camp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>Which historical camp is used for ceremonial purposes?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,21 +814,159 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>page_14</t>
+          <t>trade_camp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Historical Camps Knowledge Quiz</t>
+          <t>Which historical camp was built for the purpose of trade?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>camp_location</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>In which region is the majority of historical camps located?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>camp_height</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>What is the typical height of a historical camp?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>military_camp</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Which historical camp was used for military purposes?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>exploration_camp</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Which historical camp was built for the purpose of exploration?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>rome_camp</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Which historical camp is associated with the ancient city of Rome?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>first_historical_camp</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>What is the name of the first historical camp to be built?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -848,9 +986,9 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -873,136 +1011,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>first_historical_camp_date_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1st</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>first_historical_camp_date_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>2nd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_5_choices</t>
+          <t>first_historical_camp_date_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>3rd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_5_choices</t>
+          <t>first_historical_camp_date_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>4th</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>rome_camp_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>war_camp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>War camp</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>rome_camp_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>trade_camp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Trade camp</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>rome_camp_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>agricultural_camp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Agricultural camp</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>rome_camp_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>exploration_camp</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Exploration camp</t>
         </is>
       </c>
     </row>
